--- a/Lucknow-March-2026.xlsx
+++ b/Lucknow-March-2026.xlsx
@@ -109,7 +109,7 @@
     <t>HR55AX2090</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>DZIRE</t>
